--- a/data/site.xlsx
+++ b/data/site.xlsx
@@ -1,17 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="說明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="config" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="classes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="course_dates" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="faqs" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="說明" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="config" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="classes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="course_dates" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="faqs" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="series" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="keywords" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="about" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="refund" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="privacy" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="exp_hints" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -222,6 +228,26 @@
 </comments>
 </file>
 
+<file path=xl/comments/comment10.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>規範</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>經驗代號（須與 classes 的 experience_requirement 一致）</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>詳情頁顯示文字</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
@@ -240,7 +266,7 @@
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>所屬系列（山野成長 / 自然探索 / 原野觀察）</t>
+        <t>所屬系列（須與 series 表的 name 完全一致）</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
@@ -265,7 +291,7 @@
     </comment>
     <comment ref="H1" authorId="0" shapeId="0">
       <text>
-        <t>經驗（無 / 低頻率 / 中頻率 / 一定程度）</t>
+        <t>經驗代號（須對應 exp_hints 表的 code）</t>
       </text>
     </comment>
     <comment ref="I1" authorId="0" shapeId="0">
@@ -291,6 +317,16 @@
     <comment ref="M1" authorId="0" shapeId="0">
       <text>
         <t>顯示順序（小到大，整數）</t>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <t>價格單位（例：／每位小孩；無則留空）</t>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
+        <t>費用包含項目（顯示於詳情頁摺疊）</t>
       </text>
     </comment>
   </commentList>
@@ -361,6 +397,146 @@
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
         <t>答案（可 Alt+Enter 換行）</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>規範</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>系列代號（英數小寫，當網址錨點，例：mountain）</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>系列名稱（須與 classes 表的 series 完全一致）</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>區塊標題（例：山野成長系列 / 原野觀察教室）</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>課程頁分區副標</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>首頁系列卡片簡介</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>顯示順序（小到大，整數）</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>規範</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>顯示順序（小到大，整數）</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>關鍵字（例：自然觀察）</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>說明</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>規範</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>顯示順序（小到大，整數）</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>樣式（lead=大字 / muted=灰字 / body=內文 / emphasis=綠字重點）</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>段落文字（可 Alt+Enter 換行）</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment8.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>規範</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>顯示順序（小到大，整數）</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>退費時間（例：開課日前 21 天）</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>退費比例</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>規範</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>顯示順序（小到大，整數）</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>小標（例：蒐集目的）</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>內容（可 Alt+Enter 換行）</t>
       </text>
     </comment>
   </commentList>
@@ -657,7 +833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A36"/>
+  <dimension ref="A1:A42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -700,7 +876,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　config        ── 站台設定（LINE 連結、Email、PDF 路徑）</t>
+          <t xml:space="preserve">　config        ── 站台設定 + 全站文字（標題、按鈕、說明）</t>
         </is>
       </c>
     </row>
@@ -726,158 +902,200 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　series        ── 三大系列（首頁卡片 + 課程頁分區/錨點）</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>【新增班級的步驟】</t>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　keywords      ── 首頁「我們重視什麼」四宮格</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　1. 到 classes 表底下新增一列，填好欄位（class_id 不可重複）</t>
+          <t xml:space="preserve">　about         ── 首頁品牌故事段落</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　2. 到 course_dates 表新增該班級的每堂課日期（class_id 要一致）</t>
+          <t xml:space="preserve">　refund        ── 退費規定表</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　3. 存檔即可，網站約 5 分鐘內自動更新</t>
+          <t xml:space="preserve">　privacy       ── 個資聲明段落</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　exp_hints     ── 經驗代號對照（詳情頁顯示文字）</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>【新增 FAQ】</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　到 faqs 表新增一列，order 設大一點（例：99）就會排到最後</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>【新增班級的步驟】</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　答案內要換行，按 Alt+Enter（Mac：Option+Enter）</t>
+          <t xml:space="preserve">　1. 到 classes 表底下新增一列，填好欄位（class_id 不可重複）</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2. 到 course_dates 表新增該班級的每堂課日期（class_id 要一致）</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>【修改站台設定】</t>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3. 存檔即可，網站約 5 分鐘內自動更新</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　到 config 表，修改對應 key 的 value 欄（key 欄勿動）</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr"/>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>【新增 FAQ】</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>【常見地雷】</t>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　到 faqs 表新增一列，order 設大一點（例：99）就會排到最後</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　• class_id 一定要英數小寫（a-z 0-9 _），中文會壞</t>
+          <t xml:space="preserve">　答案內要換行，按 Alt+Enter（Mac：Option+Enter）</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　• 日期欄請保持 YYYY-MM-DD 文字格式，不要讓 Google 自動轉成 9/5/2026</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　（選欄→格式→數字→純文字，或在日期前面加一個半形單引號 ')</t>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>【修改站台設定】</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　• 每張表第 1 列是欄位名稱（程式碼依賴），請勿刪除、勿更名</t>
+          <t xml:space="preserve">　到 config 表，修改對應 key 的 value 欄（key 欄勿動）</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　• 不要刪欄、不要插欄；若需新欄請先聯絡開發者</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　• 不要新增 sheet（沒被程式讀取的 sheet 會被忽略，但保持乾淨）</t>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>【常見地雷】</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr"/>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　• class_id 一定要英數小寫（a-z 0-9 _），中文會壞</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>【欄位說明】</t>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　• 日期欄請保持 YYYY-MM-DD 文字格式，不要讓 Google 自動轉成 9/5/2026</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　每張表第 1 列的儲存格滑鼠移上去會看到該欄的說明。</t>
+          <t xml:space="preserve">　　（選欄→格式→數字→純文字，或在日期前面加一個半形單引號 ')</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">　• 每張表第 1 列是欄位名稱（程式碼依賴），請勿刪除、勿更名</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　• 不要刪欄、不要插欄；若需新欄請先聯絡開發者</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　• 不要新增 sheet（沒被程式讀取的 sheet 會被忽略，但保持乾淨）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>【欄位說明】</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　每張表第 1 列的儲存格滑鼠移上去會看到該欄的說明。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">　欄位順序、名稱與此處 site.xlsx 一致時，網站就會正常顯示。</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>最後更新：請依需要更新此處</t>
         </is>
@@ -885,6 +1103,192 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F2C744"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>display_order</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>heading</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>蒐集目的</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>個人資料（包含姓名、身分證字號、出生年月日及聯絡電話等）僅供「虎甲自然」辦理課程聯繫、保險投保及緊急聯絡使用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>資料保存</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>我們將嚴格保護學員的隱私，除非法律要求或保險公司作業需要，絕不提供給第三方機構。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>影像使用</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>課程期間所拍攝之照片、影片，將用於虎甲自然之成果展現與社群推廣。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>未成年人保護</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>公開社群與宣傳素材中，不會主動揭露未成年學員之清晰正臉。影像呈現將以側寫、背影或適當數位處理為主；若家長不希望肖像公開，請主動告知。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F2C744"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>hint</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>無戶外或爬山經驗</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>低頻率</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>低頻率戶外或爬山經驗</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>中頻率</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>中頻率戶外或爬山經驗</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>一定程度</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>一定程度戶外或爬山經驗</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -895,7 +1299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -985,6 +1389,943 @@
       <c r="C5" s="6" t="inlineStr">
         <is>
           <t>簡章下載路徑</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>site_name</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>虎甲自然</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>網站名稱（logo 文字）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>nav_home</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>企業概述</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>導覽列：首頁</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>nav_courses</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>課程介紹</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>導覽列：課程</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>nav_contact</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>聯絡我們</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>導覽列：聯絡</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>nav_download</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>檔案下載</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>導覽列：下載</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>nav_line</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>加 LINE</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>導覽列：右上 LINE 按鈕</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>footer_pdf_label</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>下載 PDF 簡章</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>頁尾：PDF 連結文字</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>footer_copyright</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>© 虎甲自然 Tiger Beetle Nature · 城市與自然的引路者</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>頁尾版權文字</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>home_hero_title</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>城市與自然的
+引路者</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>首頁主標（\n=換行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>home_hero_subtitle</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>陪孩子走進步道，
+成為大自然的學生</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>首頁副標（\n=換行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>home_hero_courses_btn</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>看課程介紹</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>首頁 hero 按鈕：課程</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>home_hero_line_btn</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>加 LINE 諮詢</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>首頁 hero 按鈕：LINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>home_about_heading</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>關於虎甲自然</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>首頁：品牌故事標題</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>home_about_subtitle</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>城市與自然之間，需要一位引路者</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>首頁：品牌故事副標</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>home_about_more</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>閱讀完整故事</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>首頁：展開故事按鈕</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>home_series_heading</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>三大課程系列</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>首頁：系列區標題</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>home_series_subtitle</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>選擇適合孩子的節奏</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>首頁：系列區副標</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>home_series_cta</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>看班級 →</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>首頁：系列卡片按鈕</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>home_keywords_heading</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>我們重視什麼</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>首頁：關鍵字區標題</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>home_keywords_subtitle</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>點擊看更多</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>首頁：關鍵字區副標</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>home_cta_heading</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>想了解更多？</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>首頁：底部 CTA 標題</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>home_cta_text</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>查看常見問題，或下載完整簡章認識虎甲自然。</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>首頁：底部 CTA 說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>home_cta_faq_btn</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>相關問題</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>首頁：底部 CTA 按鈕（FAQ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>home_cta_download_btn</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>下載簡章</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>首頁：底部 CTA 按鈕（下載）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>courses_hero_title</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>課程介紹</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>課程頁：主標</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>courses_hero_subtitle</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>點班級卡片看完整課程細節</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>課程頁：副標</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>courses_calendar_heading</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>課程行事曆</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>課程頁：行事曆標題</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>courses_calendar_subtitle</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>依月份折疊，點開看當月各班級日期</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>課程頁：行事曆副標</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>courses_cta_heading</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>想多了解某個班級？</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>課程頁：底部 CTA 標題</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>courses_cta_text</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>加入 LINE 與我們聯繫，或下載完整簡章。</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>課程頁：底部 CTA 說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>courses_cta_line_btn</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>加 LINE 諮詢</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>課程頁：底部 CTA 按鈕（LINE）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>courses_cta_download_btn</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>下載簡章</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>課程頁：底部 CTA 按鈕（下載）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>class_card_more</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>看詳情</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>課程卡片：看詳情按鈕</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>class_modal_fee_summary</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>費用包含項目</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>課程詳情：費用包含 摺疊標題</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>class_dates_empty</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>尚未公布日期</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>課程詳情：無日期時顯示</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>class_list_empty</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>本系列暫無班級</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>課程頁：系列無班級時顯示</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>calendar_empty</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>尚未公布行事曆</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>課程頁：行事曆無資料時顯示</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>info_hero_title</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>相關問題</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>問題頁：主標</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>info_hero_subtitle</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>常見問題、退費規定、個資聲明、聯絡與簡章下載</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>問題頁：副標</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>info_faq_heading</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>常見問題</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>問題頁：FAQ 標題</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>info_refund_heading</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>退費規定</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>問題頁：退費標題</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>info_refund_intro</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>本課程為系列課程，為保障師生權益與保險辦理，依開課日與退費階段不同有對應比例。</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>問題頁：退費前言</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>info_refund_summary</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>查看完整退費規定（4 階段）</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>問題頁：退費摺疊標題</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>info_refund_note</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>行政院公告天災或其他不可抗力因素取消，將另行協議補課日期。</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>問題頁：退費補充說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>info_refund_col_time</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>退費時間</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>問題頁：退費表欄一</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>info_refund_col_ratio</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>退費比例</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>問題頁：退費表欄二</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>info_privacy_heading</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>個人資料保護聲明</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>問題頁：個資標題</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>info_privacy_intro</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>我們蒐集的個資僅供課程聯繫、保險投保及緊急聯絡使用，絕不提供給第三方。</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>問題頁：個資前言</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>info_privacy_summary</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>查看完整聲明</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>問題頁：個資摺疊標題</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>info_contact_heading</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>聯絡我們</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>問題頁：聯絡標題</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>info_contact_line_btn</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>加 LINE 諮詢</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>問題頁：聯絡 LINE 按鈕</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>info_contact_email_btn</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>來信詢問</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>問題頁：聯絡 Email 按鈕</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>info_download_heading</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>檔案下載</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>問題頁：下載標題</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>info_pdf_title</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>虎甲自然完整簡章 PDF</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>問題頁：PDF 卡片標題</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>info_pdf_hint</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>完整版本，可分享給其他家長</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>問題頁：PDF 卡片說明</t>
         </is>
       </c>
     </row>
@@ -1001,7 +2342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1017,6 +2358,8 @@
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="40" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="50" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1085,6 +2428,16 @@
           <t>display_order</t>
         </is>
       </c>
+      <c r="N1" s="5" t="inlineStr">
+        <is>
+          <t>price_unit</t>
+        </is>
+      </c>
+      <c r="O1" s="5" t="inlineStr">
+        <is>
+          <t>fee_included</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -1152,6 +2505,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N2" s="6" t="inlineStr"/>
+      <c r="O2" s="6" t="inlineStr">
+        <is>
+          <t>專業師資、器材設備、意外保險、接駁車（視班別）。午餐、行動糧、大眾交通車資須自理。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -1219,6 +2578,12 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N3" s="6" t="inlineStr"/>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>專業師資、器材設備、意外保險、接駁車（視班別）。午餐、行動糧、大眾交通車資須自理。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -1286,6 +2651,12 @@
           <t>3</t>
         </is>
       </c>
+      <c r="N4" s="6" t="inlineStr"/>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>專業師資、器材設備、意外保險、接駁車（視班別）。午餐、行動糧、大眾交通車資須自理。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -1353,6 +2724,12 @@
           <t>4</t>
         </is>
       </c>
+      <c r="N5" s="6" t="inlineStr"/>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>專業師資、器材設備、意外保險、接駁車（視班別）。午餐、行動糧、大眾交通車資須自理。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -1420,6 +2797,12 @@
           <t>5</t>
         </is>
       </c>
+      <c r="N6" s="6" t="inlineStr"/>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
+          <t>專業師資、器材設備、意外保險、接駁車（1 次）。午餐、行動糧、大眾交通車資須自理。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -1487,6 +2870,12 @@
           <t>6</t>
         </is>
       </c>
+      <c r="N7" s="6" t="inlineStr"/>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>專業師資、器材設備、意外保險、接駁車（1–2 次）。午餐、行動糧、大眾交通車資須自理。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -1554,6 +2943,16 @@
           <t>7</t>
         </is>
       </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>／每位小孩</t>
+        </is>
+      </c>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>專業師資、器材設備、意外保險。行動糧、交通自理。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -1619,6 +3018,12 @@
       <c r="M9" s="6" t="inlineStr">
         <is>
           <t>8</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr"/>
+      <c r="O9" s="6" t="inlineStr">
+        <is>
+          <t>專業師資、器材設備、意外保險。午餐、行動糧與大眾交通自理。</t>
         </is>
       </c>
     </row>
@@ -2956,4 +4361,542 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F2C744"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>series_id</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>tagline</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>preview_desc</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>display_order</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>mountain</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>山野成長</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>山野成長系列</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>戶外自主行動 · 每月一次 · 五個月為一期</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>戶外自主行動。每月一次，五個月為一期。</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>nature</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>自然探索</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>自然探索系列</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>親子自然共學 · 兩月一次 · 六個月為一期</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>親子自然共學。兩月一次，六個月為一期。</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>原野觀察</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>原野觀察教室</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>森林修補紀實 · 每月一次 · 五個月為一期</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>森林修補紀實。主題探究與公民科學。</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F2C744"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>display_order</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>自然觀察</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>辨識植物、昆蟲，理解山林裡的生命網絡</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>人文歷史</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>尋找步道上的歷史痕跡，理解人與土地的關係</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>登山技能</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>裝備、體能、路線判讀，建立自主行動能力</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>風險意識</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>天氣、地形、時間判斷，從小培養安全意識</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F2C744"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>display_order</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>style</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>這座島嶼從海平面到 4000 公尺，氣候多元、生態豐富。我們生活在城市裡，抬頭就看見遠方山稜線，卻對山裡的人們與森林中的生命所知不多。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>muted</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>我們希望像虎甲蟲一樣，在自然與城市之間，成為「引路者」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>虎甲蟲（Tiger Beetle）是一種經常可以在步道上觀察到的昆蟲。牠時常隨著我們腳步走近，便往前飛躍一小段；週而復始，彷彿帶著我們在這條路上前進。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>這座面積僅 3 萬 6 千平方公里的島嶼——臺灣——是我們長大的地方。她被山林環抱，在極短的距離裡，從海平面攀升到將近 4000 公尺，讓她成為生物多樣性極為豐富的自然寶庫。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>近年來，伴隨山林開放政策與商業登山活絡，大幅度降低了人們接近山林的成本，但各種山難、步道耗損與環境衝擊，不斷提醒我們：不能只做單方面的環境消費者。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>在虎甲自然的帶領下，登山不只是攻頂看大景：透過自然觀察與戶外探索，我們結合「山野教育」與「環境教育」，在走進步道的過程，認識山上的植物、昆蟲，爬梳歷史、尋找人文痕跡。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>emphasis</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>山是一座無垠的教室，步道是通往教室的走廊，請跟著我們一同成為大自然的學生。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F2C744"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>display_order</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>stage</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>開課日前 21 天</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>扣除行政作業費 $200 後全額退費</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>開課日前 7–20 天</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>退還實付總額 90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>開課日前 1–6 天</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>退還實付總額 60%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>課程開始後未逾 1/3</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>退還實付總額 20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>課程進行逾 1/3</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>恕不退費</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
 </file>
--- a/data/site.xlsx
+++ b/data/site.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="說明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="config" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="classes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="course_dates" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="faqs" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="series" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="keywords" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="about" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="refund" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="privacy" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="exp_hints" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="說明" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="config" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="classes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="course_dates" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="faqs" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="series" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="keywords" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="about" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="refund" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="privacy" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="exp_hints" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,6 +51,18 @@
       <b val="1"/>
       <color rgb="002D5F3F"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Noto Sans TC"/>
+      <b val="1"/>
+      <color rgb="002D5F3F"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Noto Sans TC"/>
+      <b val="1"/>
+      <color rgb="002D5F3F"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Noto Sans TC"/>
@@ -107,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -121,10 +133,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -236,12 +254,12 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>經驗代號（須與 classes 的 experience_requirement 一致）</t>
+        <t>經驗代號（須與 classes.experience_requirement 一致）</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>詳情頁顯示文字</t>
+        <t>顯示文字（例：低頻率戶外或爬山經驗）</t>
       </text>
     </comment>
   </commentList>
@@ -256,7 +274,7 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>班級代號（英數，僅限 a-z 0-9 _，不可重複）</t>
+        <t>班級代號（英數小寫，不可重複）</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
@@ -266,32 +284,32 @@
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>所屬系列（須與 series 表的 name 完全一致）</t>
+        <t>所屬系列（須與 series.name 完全一致）</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>難度（初階 / 中階 / 進階 / 挑戰 / 親子 / 探究）</t>
+        <t>難度（初階/中階/進階/挑戰/親子/探究）</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>地區（台北 / 台中 / 宜蘭 ...）</t>
+        <t>地區</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>費用（整數，純數字）</t>
+        <t>費用（整數）</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
-        <t>年齡層（例：小一~小三）</t>
+        <t>年齡層</t>
       </text>
     </comment>
     <comment ref="H1" authorId="0" shapeId="0">
       <text>
-        <t>經驗代號（須對應 exp_hints 表的 code）</t>
+        <t>經驗代號（須對應 exp_hints.code）</t>
       </text>
     </comment>
     <comment ref="I1" authorId="0" shapeId="0">
@@ -301,12 +319,12 @@
     </comment>
     <comment ref="J1" authorId="0" shapeId="0">
       <text>
-        <t>交通說明（例：大眾交通為主）</t>
+        <t>交通說明</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>活動範圍（用、頓號或逗號分隔）</t>
+        <t>活動範圍</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -326,7 +344,7 @@
     </comment>
     <comment ref="O1" authorId="0" shapeId="0">
       <text>
-        <t>費用包含項目（顯示於詳情頁摺疊）</t>
+        <t>費用包含項目（詳情頁摺疊；留空則不顯示）</t>
       </text>
     </comment>
   </commentList>
@@ -341,7 +359,7 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>班級代號（必須與 classes 表的 class_id 完全一致）</t>
+        <t>班級代號（須與 classes.class_id 一致）</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
@@ -351,7 +369,7 @@
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>日期（YYYY-MM-DD，例：2026-09-05）</t>
+        <t>日期（YYYY-MM-DD，純文字）</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
@@ -366,7 +384,7 @@
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>備註（可空，例：含接駁包車）</t>
+        <t>備註（可空）</t>
       </text>
     </comment>
   </commentList>
@@ -386,7 +404,7 @@
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>分類（退費 / 報名 / 安全 …）</t>
+        <t>分類（退費／報名／安全 …）</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
@@ -416,12 +434,12 @@
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>系列名稱（須與 classes 表的 series 完全一致）</t>
+        <t>系列名稱（須與 classes.series 一致）</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>區塊標題（例：山野成長系列 / 原野觀察教室）</t>
+        <t>區塊標題（例：山野成長系列）</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
@@ -436,7 +454,7 @@
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>顯示順序（小到大，整數）</t>
+        <t>顯示順序</t>
       </text>
     </comment>
   </commentList>
@@ -451,7 +469,7 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>顯示順序（小到大，整數）</t>
+        <t>顯示順序</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
@@ -461,7 +479,7 @@
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>說明</t>
+        <t>說明（點擊展開時顯示）</t>
       </text>
     </comment>
   </commentList>
@@ -476,12 +494,12 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>顯示順序（小到大，整數）</t>
+        <t>顯示順序</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>樣式（lead=大字 / muted=灰字 / body=內文 / emphasis=綠字重點）</t>
+        <t>樣式：lead/muted（常顯）、body/emphasis（收進「閱讀完整故事」）</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
@@ -501,17 +519,17 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>顯示順序（小到大，整數）</t>
+        <t>顯示順序</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>退費時間（例：開課日前 21 天）</t>
+        <t>退費階段（例：開課日前 21 天）</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>退費比例</t>
+        <t>退費比例（例：扣除行政費 $200 後全額退費）</t>
       </text>
     </comment>
   </commentList>
@@ -526,17 +544,17 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>顯示順序（小到大，整數）</t>
+        <t>顯示順序</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>小標（例：蒐集目的）</t>
+        <t>小節標題（例：蒐集目的）</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>內容（可 Alt+Enter 換行）</t>
+        <t>段落內容（可 Alt+Enter 換行）</t>
       </text>
     </comment>
   </commentList>
@@ -833,10 +851,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A42"/>
+  <dimension ref="A1:A68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -876,7 +894,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　config        ── 站台設定 + 全站文字（標題、按鈕、說明）</t>
+          <t xml:space="preserve">　config        ── 站台設定 + 全站文字（key/value/note）</t>
         </is>
       </c>
     </row>
@@ -890,7 +908,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　course_dates  ── 課程日期（一列一堂，用 class_id 關聯到班級）</t>
+          <t xml:space="preserve">　course_dates  ── 課程日期（一列一堂，用 class_id 關聯班級）</t>
         </is>
       </c>
     </row>
@@ -904,14 +922,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　series        ── 三大系列（首頁卡片 + 課程頁分區/錨點）</t>
+          <t xml:space="preserve">　series        ── 三大系列（首頁卡片 + 課程頁分區）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　keywords      ── 首頁「我們重視什麼」四宮格</t>
+          <t xml:space="preserve">　keywords      ── 首頁四宮格</t>
         </is>
       </c>
     </row>
@@ -939,7 +957,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　exp_hints     ── 經驗代號對照（詳情頁顯示文字）</t>
+          <t xml:space="preserve">　exp_hints     ── 經驗代號對照</t>
         </is>
       </c>
     </row>
@@ -949,28 +967,28 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>【新增班級的步驟】</t>
+          <t>【規格驅動原則】</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　1. 到 classes 表底下新增一列，填好欄位（class_id 不可重複）</t>
+          <t xml:space="preserve">　HTML 不寫任何文案，全部文字來自這份表。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　2. 到 course_dates 表新增該班級的每堂課日期（class_id 要一致）</t>
+          <t xml:space="preserve">　程式只負責渲染，不寫任何商業邏輯（系列分區、價格單位等都看欄位）。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　3. 存檔即可，網站約 5 分鐘內自動更新</t>
+          <t xml:space="preserve">　漏鍵不會壞掉：HTML 內保留一份 fallback 原文。</t>
         </is>
       </c>
     </row>
@@ -980,90 +998,86 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>【新增 FAQ】</t>
+          <t>【新增班級的步驟】</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　到 faqs 表新增一列，order 設大一點（例：99）就會排到最後</t>
+          <t xml:space="preserve">　1. classes 新增一列，填好 15 欄（class_id 不可重複；series 須對得到 series.name）</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　答案內要換行，按 Alt+Enter（Mac：Option+Enter）</t>
+          <t xml:space="preserve">　2. course_dates 新增該班的每堂課（class_id 要一致）</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr"/>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3. 存檔即可，網站約 5 分鐘內自動更新</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>【修改站台設定】</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　到 config 表，修改對應 key 的 value 欄（key 欄勿動）</t>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>【新增系列】</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr"/>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　series 新增一列（取好 series_id），首頁與課程頁都會自動長出。</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>【常見地雷】</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　• class_id 一定要英數小寫（a-z 0-9 _），中文會壞</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>【新增 FAQ／退費規定／個資段／關鍵字／故事段落】</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　• 日期欄請保持 YYYY-MM-DD 文字格式，不要讓 Google 自動轉成 9/5/2026</t>
+          <t xml:space="preserve">　到對應 sheet 新增一列即可。display_order 設大一點就會排到最後。</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　（選欄→格式→數字→純文字，或在日期前面加一個半形單引號 ')</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　• 每張表第 1 列是欄位名稱（程式碼依賴），請勿刪除、勿更名</t>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>【修改站台設定／文字】</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　• 不要刪欄、不要插欄；若需新欄請先聯絡開發者</t>
+          <t xml:space="preserve">　到 config 表改 value 欄；key 欄勿動。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　• 不要新增 sheet（沒被程式讀取的 sheet 會被忽略，但保持乾淨）</t>
+          <t xml:space="preserve">　多行文字（home_hero_title 等）用 \n 代表換行。</t>
         </is>
       </c>
     </row>
@@ -1071,23 +1085,23 @@
       <c r="A37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>【欄位說明】</t>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>【⚠️ 資安守則 — 開動前務必讀】</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　每張表第 1 列的儲存格滑鼠移上去會看到該欄的說明。</t>
+          <t xml:space="preserve">　這份試算表上傳到 Google Drive 後會被全網路讀取。</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　欄位順序、名稱與此處 site.xlsx 一致時，網站就會正常顯示。</t>
+          <t xml:space="preserve">　網站把試算表 ID 寫在 JS 裡（任何訪客都能看到），所以 ID = 公開的入口。</t>
         </is>
       </c>
     </row>
@@ -1095,9 +1109,175 @@
       <c r="A41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>最後更新：請依需要更新此處</t>
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　🔴 絕對不要放進這份試算表：</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　• 學員 / 家長個資（姓名、電話、身分證、緊急聯絡）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　• 信用卡、銀行帳號、轉帳記錄</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　• 內部成本、毛利、講師時薪</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　• 講師私人事由、未公開的取消預定</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　• API token、密碼、LINE Channel Token</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　⚠️ 重要：在同一份試算表新增一個「內部用」sheet 不會保密。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　即使網站不去讀，任何人用以下 URL 都能直接抓走：</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　https://docs.google.com/spreadsheets/d/{ID}/gviz/tq?tqx=out:csv&amp;sheet={名稱}</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　✅ 內部資料請用「另一份完全分開」的試算表：</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　• 在 Google Drive 另建獨立檔案</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　• 分享 = 「指定 email 邀請」，不可用「擁有連結者」</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　• 該 ID 永遠不寫進 site-config.js 或任何網站檔案</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　新增資料前的 3 題自我檢查：</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　1. 被截圖貼到 FB 社團我會困擾嗎？會 → 不要放這裡</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　2. 涉及第三方（學員、講師、合作場地）嗎？涉及 → 不要放這裡</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　3. 必須讓全網看到嗎？不必 → 不要放這裡</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>【常見地雷】</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　• class_id、series_id 必須英數小寫，中文會壞</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　• 跨表關聯要一致：classes.series ↔ series.name、course_dates.class_id ↔ classes.class_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　• 日期欄保持 YYYY-MM-DD 純文字（選欄→格式→數字→純文字）</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　• 各表第 1 列欄位名不可改、不可刪欄插欄</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　• 新增 sheet 沒關係（程式只讀指定 10 張），但仍會被公網讀取（見上方資安守則）</t>
         </is>
       </c>
     </row>
@@ -1117,90 +1297,90 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>display_order</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>heading</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>body</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>蒐集目的</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>個人資料（包含姓名、身分證字號、出生年月日及聯絡電話等）僅供「虎甲自然」辦理課程聯繫、保險投保及緊急聯絡使用。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>資料保存</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>我們將嚴格保護學員的隱私，除非法律要求或保險公司作業需要，絕不提供給第三方機構。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>影像使用</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>課程期間所拍攝之照片、影片，將用於虎甲自然之成果展現與社群推廣。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>未成年人保護</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>公開社群與宣傳素材中，不會主動揭露未成年學員之清晰正臉。影像呈現將以側寫、背影或適當數位處理為主；若家長不希望肖像公開，請主動告知。</t>
         </is>
@@ -1222,65 +1402,65 @@
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>hint</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>無</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>無戶外或爬山經驗</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>低頻率</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>低頻率戶外或爬山經驗</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>中頻率</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>中頻率戶外或爬山經驗</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>一定程度</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>一定程度戶外或爬山經驗</t>
         </is>
@@ -1299,1031 +1479,1133 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>line_oa_url</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>https://lin.ee/TPOEska</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>LINE 加入連結</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>line_oa_id</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>@821lvzed</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>LINE 官方帳號 ID</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>contact_email</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>bill541328@tbnature.com.tw</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>聯絡信箱</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>pdf_url</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>assets/tiger-beetle-2026.pdf</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>簡章下載路徑</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>site_name</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>虎甲自然</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>網站名稱（logo 文字）</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>nav_home</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>企業概述</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>導覽列：首頁</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>nav_courses</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>課程介紹</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>導覽列：課程</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>nav_contact</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>聯絡我們</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>導覽列：聯絡</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>nav_download</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>檔案下載</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>導覽列：下載</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>nav_line</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>加 LINE</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>導覽列：右上 LINE 按鈕</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>footer_pdf_label</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>下載 PDF 簡章</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>頁尾：PDF 連結文字</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>footer_copyright</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>© 虎甲自然 Tiger Beetle Nature · 城市與自然的引路者</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>頁尾版權文字</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>home_hero_title</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>城市與自然的
 引路者</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>首頁主標（\n=換行）</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>home_hero_subtitle</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>陪孩子走進步道，
 成為大自然的學生</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>首頁副標（\n=換行）</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>home_hero_courses_btn</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>看課程介紹</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>首頁 hero 按鈕：課程</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>home_hero_line_btn</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>加 LINE 諮詢</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>首頁 hero 按鈕：LINE</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>register_url</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSdYiOmhPcmSpGkzhIr9cGwcwpl1vM6H52QdZGP3AW_nj55A8Q/viewform</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>線上報名 Google Form 連結</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>home_hero_register_btn</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>立即報名</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>首頁 hero 按鈕：報名</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>home_about_heading</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>關於虎甲自然</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>首頁：品牌故事標題</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>home_about_subtitle</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>城市與自然之間，需要一位引路者</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>首頁：品牌故事副標</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>home_about_more</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>閱讀完整故事</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>首頁：展開故事按鈕</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>home_series_heading</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>三大課程系列</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>首頁：系列區標題</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>home_series_subtitle</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>選擇適合孩子的節奏</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>首頁：系列區副標</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>home_series_cta</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>看班級 →</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>首頁：系列卡片按鈕</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>home_keywords_heading</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>我們重視什麼</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>首頁：關鍵字區標題</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>home_keywords_subtitle</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>點擊看更多</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>首頁：關鍵字區副標</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>home_cta_heading</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>想了解更多？</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>首頁：底部 CTA 標題</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>home_cta_text</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>查看常見問題，或下載完整簡章認識虎甲自然。</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>首頁：底部 CTA 說明</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>home_cta_faq_btn</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>相關問題</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>首頁：底部 CTA 按鈕（FAQ）</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>home_cta_download_btn</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>下載簡章</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>首頁：底部 CTA 按鈕（下載）</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>home_register_heading</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>準備好走進山林了嗎？</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>首頁：報名區標題</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>home_register_text</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>填寫線上表單，我們會在 3 個工作天內回覆確認。</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>首頁：報名區說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>home_register_btn</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>立即報名</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>首頁：報名區按鈕</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>courses_hero_title</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>課程介紹</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>課程頁：主標</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>courses_hero_subtitle</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>點班級卡片看完整課程細節</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>課程頁：副標</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>courses_calendar_heading</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>課程行事曆</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>課程頁：行事曆標題</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>courses_calendar_subtitle</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>依月份折疊，點開看當月各班級日期</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>課程頁：行事曆副標</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>courses_cta_heading</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>想多了解某個班級？</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>課程頁：底部 CTA 標題</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>courses_cta_text</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>加入 LINE 與我們聯繫，或下載完整簡章。</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>課程頁：底部 CTA 說明</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>courses_cta_line_btn</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>加 LINE 諮詢</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>課程頁：底部 CTA 按鈕（LINE）</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>courses_cta_download_btn</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>下載簡章</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>課程頁：底部 CTA 按鈕（下載）</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>class_card_more</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>看詳情</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>課程卡片：看詳情按鈕</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>class_modal_fee_summary</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>費用包含項目</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>課程詳情：費用包含 摺疊標題</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>class_modal_register_btn</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>報名此班</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>課程詳情 Modal：報名按鈕</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>class_dates_empty</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t>尚未公布日期</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>課程詳情：無日期時顯示</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>class_list_empty</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>本系列暫無班級</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>課程頁：系列無班級時顯示</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>calendar_empty</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>尚未公布行事曆</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>課程頁：行事曆無資料時顯示</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>info_hero_title</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>相關問題</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>問題頁：主標</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>info_hero_subtitle</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t>常見問題、退費規定、個資聲明、聯絡與簡章下載</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>問題頁：副標</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>info_faq_heading</t>
         </is>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>常見問題</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C51" s="8" t="inlineStr">
         <is>
           <t>問題頁：FAQ 標題</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>info_refund_heading</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t>退費規定</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>問題頁：退費標題</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>info_refund_intro</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>本課程為系列課程，為保障師生權益與保險辦理，依開課日與退費階段不同有對應比例。</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>問題頁：退費前言</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>info_refund_summary</t>
         </is>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t>查看完整退費規定（4 階段）</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t>問題頁：退費摺疊標題</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>info_refund_note</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>行政院公告天災或其他不可抗力因素取消，將另行協議補課日期。</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>問題頁：退費補充說明</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>info_refund_col_time</t>
         </is>
       </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>退費時間</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>問題頁：退費表欄一</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
         <is>
           <t>info_refund_col_ratio</t>
         </is>
       </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>退費比例</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t>問題頁：退費表欄二</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>info_privacy_heading</t>
         </is>
       </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t>個人資料保護聲明</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
+      <c r="C58" s="8" t="inlineStr">
         <is>
           <t>問題頁：個資標題</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>info_privacy_intro</t>
         </is>
       </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>我們蒐集的個資僅供課程聯繫、保險投保及緊急聯絡使用，絕不提供給第三方。</t>
         </is>
       </c>
-      <c r="C53" s="6" t="inlineStr">
+      <c r="C59" s="8" t="inlineStr">
         <is>
           <t>問題頁：個資前言</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>info_privacy_summary</t>
         </is>
       </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>查看完整聲明</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t>問題頁：個資摺疊標題</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>info_contact_heading</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>聯絡我們</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C61" s="8" t="inlineStr">
         <is>
           <t>問題頁：聯絡標題</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
         <is>
           <t>info_contact_line_btn</t>
         </is>
       </c>
-      <c r="B56" s="6" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>加 LINE 諮詢</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>問題頁：聯絡 LINE 按鈕</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
         <is>
           <t>info_contact_email_btn</t>
         </is>
       </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>來信詢問</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>問題頁：聯絡 Email 按鈕</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
         <is>
           <t>info_download_heading</t>
         </is>
       </c>
-      <c r="B58" s="6" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>檔案下載</t>
         </is>
       </c>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="C64" s="8" t="inlineStr">
         <is>
           <t>問題頁：下載標題</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="6" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
         <is>
           <t>info_pdf_title</t>
         </is>
       </c>
-      <c r="B59" s="6" t="inlineStr">
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>虎甲自然完整簡章 PDF</t>
         </is>
       </c>
-      <c r="C59" s="6" t="inlineStr">
+      <c r="C65" s="8" t="inlineStr">
         <is>
           <t>問題頁：PDF 卡片標題</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
         <is>
           <t>info_pdf_hint</t>
         </is>
       </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>完整版本，可分享給其他家長</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C66" s="8" t="inlineStr">
         <is>
           <t>問題頁：PDF 卡片說明</t>
         </is>
@@ -2358,670 +2640,670 @@
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="40" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="50" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>class_id</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>series</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>age_range</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>experience_requirement</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>duration_hours</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>transport_note</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>activity_areas</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>display_order</t>
         </is>
       </c>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="N1" s="7" t="inlineStr">
         <is>
           <t>price_unit</t>
         </is>
       </c>
-      <c r="O1" s="5" t="inlineStr">
+      <c r="O1" s="7" t="inlineStr">
         <is>
           <t>fee_included</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>shanshi</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>山柿班</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>山野成長</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>初階</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>台北</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>8000</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>小一~小三</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="8" t="inlineStr">
         <is>
           <t>無</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="I2" s="8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="J2" s="8" t="inlineStr">
         <is>
           <t>大眾交通為主</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="K2" s="8" t="inlineStr">
         <is>
           <t>台北大安、士林、北投、新北鶯歌</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="L2" s="8" t="inlineStr">
         <is>
           <t>適合無戶外經驗的孩子，從鄰近郊山開始建立基礎山野能力。</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="M2" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N2" s="6" t="inlineStr"/>
-      <c r="O2" s="6" t="inlineStr">
+      <c r="N2" s="8" t="inlineStr"/>
+      <c r="O2" s="8" t="inlineStr">
         <is>
           <t>專業師資、器材設備、意外保險、接駁車（視班別）。午餐、行動糧、大眾交通車資須自理。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>kulian</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>苦楝班</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>山野成長</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>初階</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>台中</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>8000</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>小一~小三</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>無</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="I3" s="8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="J3" s="8" t="inlineStr">
         <is>
           <t>大眾交通為主</t>
         </is>
       </c>
-      <c r="K3" s="6" t="inlineStr">
+      <c r="K3" s="8" t="inlineStr">
         <is>
           <t>台中新社、大肚、太平、烏日、潭子</t>
         </is>
       </c>
-      <c r="L3" s="6" t="inlineStr">
+      <c r="L3" s="8" t="inlineStr">
         <is>
           <t>中台灣的初階班，走進新社、大肚台地，認識中部低海拔自然。</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="M3" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N3" s="6" t="inlineStr"/>
-      <c r="O3" s="6" t="inlineStr">
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="inlineStr">
         <is>
           <t>專業師資、器材設備、意外保險、接駁車（視班別）。午餐、行動糧、大眾交通車資須自理。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>fengxiang</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>風箱班</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>山野成長</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>初階</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>宜蘭</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>8000</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>小一~小三</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>無</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="J4" s="8" t="inlineStr">
         <is>
           <t>大眾交通為主</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>新北貢寮、宜蘭頭城、礁溪、蘇澳、南澳</t>
         </is>
       </c>
-      <c r="L4" s="6" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>東北角海岸與蘭陽平原，從海到山的多樣地形體驗。</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="M4" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N4" s="6" t="inlineStr"/>
-      <c r="O4" s="6" t="inlineStr">
+      <c r="N4" s="8" t="inlineStr"/>
+      <c r="O4" s="8" t="inlineStr">
         <is>
           <t>專業師資、器材設備、意外保險、接駁車（視班別）。午餐、行動糧、大眾交通車資須自理。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>xiangnan</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>香楠班</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>山野成長</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>中階</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>台北</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>8500</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>小二~小五</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>低頻率</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="J5" s="8" t="inlineStr">
         <is>
           <t>大眾交通為主</t>
         </is>
       </c>
-      <c r="K5" s="6" t="inlineStr">
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t>台北內湖、士林、新北中和、土城</t>
         </is>
       </c>
-      <c r="L5" s="6" t="inlineStr">
+      <c r="L5" s="8" t="inlineStr">
         <is>
           <t>一年以上戶外經驗的孩子，更多自主行動與環境理解。</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr">
+      <c r="M5" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N5" s="6" t="inlineStr"/>
-      <c r="O5" s="6" t="inlineStr">
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="inlineStr">
         <is>
           <t>專業師資、器材設備、意外保險、接駁車（視班別）。午餐、行動糧、大眾交通車資須自理。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>fengxiang_maple</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>楓香班</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>山野成長</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>進階</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>台北</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>9500</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>小三~小六</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>中頻率</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="J6" s="8" t="inlineStr">
         <is>
           <t>大眾交通為主，含一次接駁包車</t>
         </is>
       </c>
-      <c r="K6" s="6" t="inlineStr">
+      <c r="K6" s="8" t="inlineStr">
         <is>
           <t>台北北投、南港、新北八里、鶯歌、烏來、瑞芳</t>
         </is>
       </c>
-      <c r="L6" s="6" t="inlineStr">
+      <c r="L6" s="8" t="inlineStr">
         <is>
           <t>強化自主行動與環境應變，活動範圍擴及大台北郊山。</t>
         </is>
       </c>
-      <c r="M6" s="6" t="inlineStr">
+      <c r="M6" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N6" s="6" t="inlineStr"/>
-      <c r="O6" s="6" t="inlineStr">
+      <c r="N6" s="8" t="inlineStr"/>
+      <c r="O6" s="8" t="inlineStr">
         <is>
           <t>專業師資、器材設備、意外保險、接駁車（1 次）。午餐、行動糧、大眾交通車資須自理。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>lengshan</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>冷杉班</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>山野成長</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>挑戰</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>台北</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>10500</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>小六~國中</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>一定程度</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="J7" s="8" t="inlineStr">
         <is>
           <t>大眾交通為主，含一~二次接駁包車</t>
         </is>
       </c>
-      <c r="K7" s="6" t="inlineStr">
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t>台北內湖、士林、南港、新北新店、三峽、烏來</t>
         </is>
       </c>
-      <c r="L7" s="6" t="inlineStr">
+      <c r="L7" s="8" t="inlineStr">
         <is>
           <t>挑戰百岳與夜間登山，寒暑假百岳營隊優先參與。</t>
         </is>
       </c>
-      <c r="M7" s="6" t="inlineStr">
+      <c r="M7" s="8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="N7" s="6" t="inlineStr"/>
-      <c r="O7" s="6" t="inlineStr">
+      <c r="N7" s="8" t="inlineStr"/>
+      <c r="O7" s="8" t="inlineStr">
         <is>
           <t>專業師資、器材設備、意外保險、接駁車（1–2 次）。午餐、行動糧、大眾交通車資須自理。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>shoucao</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>綬草班</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>自然探索</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>親子</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>台北</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>2400</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>中班~小三</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>無</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" s="6" t="inlineStr">
+      <c r="J8" s="8" t="inlineStr">
         <is>
           <t>大眾交通自理</t>
         </is>
       </c>
-      <c r="K8" s="6" t="inlineStr">
+      <c r="K8" s="8" t="inlineStr">
         <is>
           <t>台北大安、士林、北投、文山、新店</t>
         </is>
       </c>
-      <c r="L8" s="6" t="inlineStr">
+      <c r="L8" s="8" t="inlineStr">
         <is>
           <t>親子共學，每兩個月一次週五下半天，由家長陪同走進近郊步道。</t>
         </is>
       </c>
-      <c r="M8" s="6" t="inlineStr">
+      <c r="M8" s="8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N8" s="6" t="inlineStr">
+      <c r="N8" s="8" t="inlineStr">
         <is>
           <t>／每位小孩</t>
         </is>
       </c>
-      <c r="O8" s="6" t="inlineStr">
+      <c r="O8" s="8" t="inlineStr">
         <is>
           <t>專業師資、器材設備、意外保險。行動糧、交通自理。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>yuteng</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>魚藤班</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>原野觀察</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>探究</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>台北</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>9500</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>小四以上</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>無</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J9" s="6" t="inlineStr">
+      <c r="J9" s="8" t="inlineStr">
         <is>
           <t>大眾交通自理</t>
         </is>
       </c>
-      <c r="K9" s="6" t="inlineStr">
+      <c r="K9" s="8" t="inlineStr">
         <is>
           <t>大台北地區，含部分室內課</t>
         </is>
       </c>
-      <c r="L9" s="6" t="inlineStr">
+      <c r="L9" s="8" t="inlineStr">
         <is>
           <t>主題探究與公民科學，從趴溪到夜間觀察，動手做森林修補。</t>
         </is>
       </c>
-      <c r="M9" s="6" t="inlineStr">
+      <c r="M9" s="8" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N9" s="6" t="inlineStr"/>
-      <c r="O9" s="6" t="inlineStr">
+      <c r="N9" s="8" t="inlineStr"/>
+      <c r="O9" s="8" t="inlineStr">
         <is>
           <t>專業師資、器材設備、意外保險。午餐、行動糧與大眾交通自理。</t>
         </is>
@@ -3052,1120 +3334,1120 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>class_id</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>session_no</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>weekday</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>time_period</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>shanshi</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>六</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr"/>
+      <c r="F2" s="8" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>shanshi</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>六</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>shanshi</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>2026-11-07</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>六</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr"/>
+      <c r="F4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>shanshi</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>2026-12-05</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>六</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>shanshi</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>2027-01-23</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>六</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>kulian</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>六</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr"/>
+      <c r="F7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>kulian</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>六</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr"/>
+      <c r="F8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>kulian</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>2026-11-14</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>六</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>kulian</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>2026-12-12</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>六</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr"/>
+      <c r="F10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>kulian</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>2027-01-09</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>六</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr"/>
+      <c r="F11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>fengxiang</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>六</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr"/>
+      <c r="F12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>fengxiang</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>2026-10-31</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>六</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr"/>
+      <c r="F13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>fengxiang</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>2026-11-21</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>六</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr"/>
+      <c r="F14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>fengxiang</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>2026-12-19</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>六</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr"/>
+      <c r="F15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>fengxiang</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>2027-01-16</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>六</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr"/>
+      <c r="F16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>xiangnan</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>六</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr"/>
+      <c r="F17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>xiangnan</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>2026-10-31</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>六</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr"/>
+      <c r="F18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>xiangnan</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>2026-11-07</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>六</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr"/>
+      <c r="F19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>xiangnan</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>2026-12-05</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>六</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr"/>
+      <c r="F20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>xiangnan</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>2027-01-23</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>六</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr"/>
+      <c r="F21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>fengxiang_maple</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr"/>
+      <c r="F22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>fengxiang_maple</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr"/>
+      <c r="F23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>fengxiang_maple</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>2026-11-15</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr"/>
+      <c r="F24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>fengxiang_maple</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>2026-12-13</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr"/>
+      <c r="F25" s="8" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>fengxiang_maple</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>2027-01-10</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr"/>
+      <c r="F26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>lengshan</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr"/>
+      <c r="F27" s="8" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>lengshan</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>2026-11-01</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr"/>
+      <c r="F28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>lengshan</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>2026-11-22</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>afternoon_evening</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="F29" s="8" t="inlineStr">
         <is>
           <t>下午~晚間課程</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>lengshan</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>2026-12-20</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr"/>
+      <c r="F30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>lengshan</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>2027-01-17</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr"/>
+      <c r="F31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>shoucao</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>half_day</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="F32" s="8" t="inlineStr">
         <is>
           <t>8/14 或 9/11 擇一</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>shoucao</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t>half_day</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="F33" s="8" t="inlineStr">
         <is>
           <t>10/16 或 11/13 擇一</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>shoucao</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>2027-01-08</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>half_day</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr">
+      <c r="F34" s="8" t="inlineStr">
         <is>
           <t>12/11 或 2027/1/8 擇一</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>yuteng</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr"/>
+      <c r="F35" s="8" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>yuteng</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>afternoon_evening</t>
         </is>
       </c>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="F36" s="8" t="inlineStr">
         <is>
           <t>下午~晚間課程</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>yuteng</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>2026-11-08</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D37" s="8" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr"/>
+      <c r="F37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>yuteng</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>2026-12-06</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D38" s="8" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr"/>
+      <c r="F38" s="8" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>yuteng</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>2027-01-24</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>full_day</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr"/>
+      <c r="F39" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4184,50 +4466,50 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>question</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>answer</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>退費</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>如果報名後臨時無法參加，可以退費嗎？</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>本課程為系列課程，退費規定如下：
 • 開課日前 21 天：扣除行政作業費 $200 後全額退費
@@ -4240,22 +4522,22 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>報名</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>全勤或請假有什麼優惠？</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>• 全勤學員下一期續報，可享 10% 折扣（限本人）
 • 因個人因素請假者，下一期報名可享 5% 折扣（限本人）
@@ -4264,22 +4546,22 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>課程拍攝的照片會用在哪裡？</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>課程期間拍攝的照片與影片，將用於虎甲自然的成果展現與社群推廣。
 針對未成年學員，公開素材中不會主動揭露清晰正臉，以側寫、背影或數位處理為主。如不希望肖像公開，請於報名時主動告知。</t>
@@ -4287,22 +4569,22 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>報名</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>為什麼線上報名沒有要求身分證字號？</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>身分證字號屬於高敏感個資，為了避免線上傳輸風險，我們不在表單上收集。
 待報名確認後，我們會由 LINE 一對一個別聯繫，請您提供保險投保所需的身分證字號。</t>
@@ -4310,22 +4592,22 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>安全</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>遇到下雨或天氣不佳會怎麼處理？</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>我們會依當日氣象與步道條件，於前一晚或當日清晨評估：
 • 小雨：照常進行，請學員攜帶雨具
@@ -4335,22 +4617,22 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>課程</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>我可以中途換班或補課嗎？</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>原則上不提供換班與補課機制，請於報名前確認班級時程是否能配合。
 例外：若本期報名踴躍加開班別，可申請跨班補課，以一次為限。詳情請洽 LINE 諮詢。</t>
@@ -4376,134 +4658,134 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>series_id</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>tagline</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>preview_desc</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>display_order</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>mountain</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>山野成長</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>山野成長系列</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>戶外自主行動 · 每月一次 · 五個月為一期</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>戶外自主行動。每月一次，五個月為一期。</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>nature</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>自然探索</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>自然探索系列</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>親子自然共學 · 兩月一次 · 六個月為一期</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>親子自然共學。兩月一次，六個月為一期。</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>field</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>原野觀察</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>原野觀察教室</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>森林修補紀實 · 每月一次 · 五個月為一期</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>森林修補紀實。主題探究與公民科學。</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -4527,89 +4809,89 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>display_order</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>自然觀察</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>辨識植物、昆蟲，理解山林裡的生命網絡</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>人文歷史</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>尋找步道上的歷史痕跡，理解人與土地的關係</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>登山技能</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>裝備、體能、路線判讀，建立自主行動能力</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>風險意識</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>天氣、地形、時間判斷，從小培養安全意識</t>
         </is>
@@ -4632,141 +4914,141 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>display_order</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>style</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>lead</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>這座島嶼從海平面到 4000 公尺，氣候多元、生態豐富。我們生活在城市裡，抬頭就看見遠方山稜線，卻對山裡的人們與森林中的生命所知不多。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>muted</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>我們希望像虎甲蟲一樣，在自然與城市之間，成為「引路者」。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>body</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>虎甲蟲（Tiger Beetle）是一種經常可以在步道上觀察到的昆蟲。牠時常隨著我們腳步走近，便往前飛躍一小段；週而復始，彷彿帶著我們在這條路上前進。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>body</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>這座面積僅 3 萬 6 千平方公里的島嶼——臺灣——是我們長大的地方。她被山林環抱，在極短的距離裡，從海平面攀升到將近 4000 公尺，讓她成為生物多樣性極為豐富的自然寶庫。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>body</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>近年來，伴隨山林開放政策與商業登山活絡，大幅度降低了人們接近山林的成本，但各種山難、步道耗損與環境衝擊，不斷提醒我們：不能只做單方面的環境消費者。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>body</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>在虎甲自然的帶領下，登山不只是攻頂看大景：透過自然觀察與戶外探索，我們結合「山野教育」與「環境教育」，在走進步道的過程，認識山上的植物、昆蟲，爬梳歷史、尋找人文痕跡。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>emphasis</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>山是一座無垠的教室，步道是通往教室的走廊，請跟著我們一同成為大自然的學生。</t>
         </is>
@@ -4789,107 +5071,107 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>display_order</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>開課日前 21 天</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>扣除行政作業費 $200 後全額退費</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>開課日前 7–20 天</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>退還實付總額 90%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>開課日前 1–6 天</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>退還實付總額 60%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>課程開始後未逾 1/3</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>退還實付總額 20%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>課程進行逾 1/3</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>恕不退費</t>
         </is>

--- a/data/site.xlsx
+++ b/data/site.xlsx
@@ -1479,7 +1479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>加 LINE</t>
+          <t>回到 LINE 官方帳號</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -1694,918 +1694,935 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>footer_copyright</t>
+          <t>footer_line_label</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>© 虎甲自然 Tiger Beetle Nature · 城市與自然的引路者</t>
+          <t>回到 LINE 官方帳號</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>頁尾版權文字</t>
+          <t>頁尾：LINE 連結文字（會接上 line_oa_id）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
+          <t>footer_copyright</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>© 虎甲自然 Tiger Beetle Nature · 城市與自然的引路者</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>頁尾版權文字</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
           <t>home_hero_title</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>城市與自然的
 引路者</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>首頁主標（\n=換行）</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>home_hero_subtitle</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>陪孩子走進步道，
 成為大自然的學生</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>首頁副標（\n=換行）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>home_hero_courses_btn</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>看課程介紹</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>首頁 hero 按鈕：課程</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>home_hero_line_btn</t>
+          <t>home_hero_courses_btn</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>加 LINE 諮詢</t>
+          <t>看課程介紹</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>首頁 hero 按鈕：LINE</t>
+          <t>首頁 hero 按鈕：課程</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>register_url</t>
+          <t>home_hero_line_btn</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>https://docs.google.com/forms/d/e/1FAIpQLSdYiOmhPcmSpGkzhIr9cGwcwpl1vM6H52QdZGP3AW_nj55A8Q/viewform</t>
+          <t>回到 LINE 官方帳號</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>線上報名 Google Form 連結</t>
+          <t>首頁 hero 按鈕：LINE</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>home_hero_register_btn</t>
+          <t>register_url</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>立即報名</t>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSdYiOmhPcmSpGkzhIr9cGwcwpl1vM6H52QdZGP3AW_nj55A8Q/viewform</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>首頁 hero 按鈕：報名</t>
+          <t>線上報名 Google Form 連結</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>home_about_heading</t>
+          <t>home_hero_register_btn</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>關於虎甲自然</t>
+          <t>立即報名</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>首頁：品牌故事標題</t>
+          <t>首頁 hero 按鈕：報名</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>home_about_subtitle</t>
+          <t>home_about_heading</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>城市與自然之間，需要一位引路者</t>
+          <t>關於虎甲自然</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>首頁：品牌故事副標</t>
+          <t>首頁：品牌故事標題</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>home_about_more</t>
+          <t>home_about_subtitle</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>閱讀完整故事</t>
+          <t>城市與自然之間，需要一位引路者</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>首頁：展開故事按鈕</t>
+          <t>首頁：品牌故事副標</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>home_series_heading</t>
+          <t>home_about_more</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>三大課程系列</t>
+          <t>閱讀完整故事</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>首頁：系列區標題</t>
+          <t>首頁：展開故事按鈕</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>home_series_subtitle</t>
+          <t>home_series_heading</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>選擇適合孩子的節奏</t>
+          <t>三大課程系列</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>首頁：系列區副標</t>
+          <t>首頁：系列區標題</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>home_series_cta</t>
+          <t>home_series_subtitle</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>看班級 →</t>
+          <t>選擇適合孩子的節奏</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>首頁：系列卡片按鈕</t>
+          <t>首頁：系列區副標</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>home_keywords_heading</t>
+          <t>home_series_cta</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>我們重視什麼</t>
+          <t>看班級 →</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>首頁：關鍵字區標題</t>
+          <t>首頁：系列卡片按鈕</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>home_keywords_subtitle</t>
+          <t>home_keywords_heading</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>點擊看更多</t>
+          <t>我們重視什麼</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>首頁：關鍵字區副標</t>
+          <t>首頁：關鍵字區標題</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>home_cta_heading</t>
+          <t>home_keywords_subtitle</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>想了解更多？</t>
+          <t>點擊看更多</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>首頁：底部 CTA 標題</t>
+          <t>首頁：關鍵字區副標</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>home_cta_text</t>
+          <t>home_cta_heading</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>查看常見問題，或下載完整簡章認識虎甲自然。</t>
+          <t>想了解更多？</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>首頁：底部 CTA 說明</t>
+          <t>首頁：底部 CTA 標題</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>home_cta_faq_btn</t>
+          <t>home_cta_text</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>相關問題</t>
+          <t>查看常見問題，或下載完整簡章認識虎甲自然。</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>首頁：底部 CTA 按鈕（FAQ）</t>
+          <t>首頁：底部 CTA 說明</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>home_cta_download_btn</t>
+          <t>home_cta_faq_btn</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>下載簡章</t>
+          <t>相關問題</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>首頁：底部 CTA 按鈕（下載）</t>
+          <t>首頁：底部 CTA 按鈕（FAQ）</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>home_register_heading</t>
+          <t>home_cta_download_btn</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>準備好走進山林了嗎？</t>
+          <t>下載簡章</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>首頁：報名區標題</t>
+          <t>首頁：底部 CTA 按鈕（下載）</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>home_register_text</t>
+          <t>home_register_heading</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>填寫線上表單，我們會在 3 個工作天內回覆確認。</t>
+          <t>準備好走進山林了嗎？</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>首頁：報名區說明</t>
+          <t>首頁：報名區標題</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>home_register_btn</t>
+          <t>home_register_text</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>立即報名</t>
+          <t>填寫線上表單，我們會在 3 個工作天內回覆確認。</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>首頁：報名區按鈕</t>
+          <t>首頁：報名區說明</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>courses_hero_title</t>
+          <t>home_register_btn</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>課程介紹</t>
+          <t>立即報名</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>課程頁：主標</t>
+          <t>首頁：報名區按鈕</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>courses_hero_subtitle</t>
+          <t>courses_hero_title</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>點班級卡片看完整課程細節</t>
+          <t>課程介紹</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>課程頁：副標</t>
+          <t>課程頁：主標</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>courses_calendar_heading</t>
+          <t>courses_hero_subtitle</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>課程行事曆</t>
+          <t>點班級卡片看完整課程細節</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>課程頁：行事曆標題</t>
+          <t>課程頁：副標</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>courses_calendar_subtitle</t>
+          <t>courses_calendar_heading</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>依月份折疊，點開看當月各班級日期</t>
+          <t>課程行事曆</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>課程頁：行事曆副標</t>
+          <t>課程頁：行事曆標題</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>courses_cta_heading</t>
+          <t>courses_calendar_subtitle</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>想多了解某個班級？</t>
+          <t>依月份折疊，點開看當月各班級日期</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>課程頁：底部 CTA 標題</t>
+          <t>課程頁：行事曆副標</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>courses_cta_text</t>
+          <t>courses_cta_heading</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>加入 LINE 與我們聯繫，或下載完整簡章。</t>
+          <t>想多了解某個班級？</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>課程頁：底部 CTA 說明</t>
+          <t>課程頁：底部 CTA 標題</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>courses_cta_line_btn</t>
+          <t>courses_cta_text</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>加 LINE 諮詢</t>
+          <t>回到 LINE 一對一諮詢，或下載完整簡章。</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>課程頁：底部 CTA 按鈕（LINE）</t>
+          <t>課程頁：底部 CTA 說明</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>courses_cta_download_btn</t>
+          <t>courses_cta_line_btn</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>下載簡章</t>
+          <t>回到 LINE 官方帳號</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>課程頁：底部 CTA 按鈕（下載）</t>
+          <t>課程頁：底部 CTA 按鈕（LINE）</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>class_card_more</t>
+          <t>courses_cta_download_btn</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>看詳情</t>
+          <t>下載簡章</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>課程卡片：看詳情按鈕</t>
+          <t>課程頁：底部 CTA 按鈕（下載）</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>class_modal_fee_summary</t>
+          <t>class_card_more</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>費用包含項目</t>
+          <t>看詳情</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>課程詳情：費用包含 摺疊標題</t>
+          <t>課程卡片：看詳情按鈕</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>class_modal_register_btn</t>
+          <t>class_modal_fee_summary</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>報名此班</t>
+          <t>費用包含項目</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>課程詳情 Modal：報名按鈕</t>
+          <t>課程詳情：費用包含 摺疊標題</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>class_dates_empty</t>
+          <t>class_modal_register_btn</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>尚未公布日期</t>
+          <t>報名此班</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>課程詳情：無日期時顯示</t>
+          <t>課程詳情 Modal：報名按鈕</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>class_list_empty</t>
+          <t>class_dates_empty</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>本系列暫無班級</t>
+          <t>尚未公布日期</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>課程頁：系列無班級時顯示</t>
+          <t>課程詳情：無日期時顯示</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>calendar_empty</t>
+          <t>class_list_empty</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>尚未公布行事曆</t>
+          <t>本系列暫無班級</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>課程頁：行事曆無資料時顯示</t>
+          <t>課程頁：系列無班級時顯示</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>info_hero_title</t>
+          <t>calendar_empty</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>相關問題</t>
+          <t>尚未公布行事曆</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>問題頁：主標</t>
+          <t>課程頁：行事曆無資料時顯示</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>info_hero_subtitle</t>
+          <t>info_hero_title</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>常見問題、退費規定、個資聲明、聯絡與簡章下載</t>
+          <t>相關問題</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>問題頁：副標</t>
+          <t>問題頁：主標</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>info_faq_heading</t>
+          <t>info_hero_subtitle</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>常見問題</t>
+          <t>常見問題、退費規定、個資聲明、聯絡與簡章下載</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>問題頁：FAQ 標題</t>
+          <t>問題頁：副標</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>info_refund_heading</t>
+          <t>info_faq_heading</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>退費規定</t>
+          <t>常見問題</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>問題頁：退費標題</t>
+          <t>問題頁：FAQ 標題</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>info_refund_intro</t>
+          <t>info_refund_heading</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>本課程為系列課程，為保障師生權益與保險辦理，依開課日與退費階段不同有對應比例。</t>
+          <t>退費規定</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>問題頁：退費前言</t>
+          <t>問題頁：退費標題</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>info_refund_summary</t>
+          <t>info_refund_intro</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>查看完整退費規定（4 階段）</t>
+          <t>本課程為系列課程，為保障師生權益與保險辦理，依開課日與退費階段不同有對應比例。</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>問題頁：退費摺疊標題</t>
+          <t>問題頁：退費前言</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>info_refund_note</t>
+          <t>info_refund_summary</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>行政院公告天災或其他不可抗力因素取消，將另行協議補課日期。</t>
+          <t>查看完整退費規定（4 階段）</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>問題頁：退費補充說明</t>
+          <t>問題頁：退費摺疊標題</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>info_refund_col_time</t>
+          <t>info_refund_note</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>退費時間</t>
+          <t>行政院公告天災或其他不可抗力因素取消，將另行協議補課日期。</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>問題頁：退費表欄一</t>
+          <t>問題頁：退費補充說明</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>info_refund_col_ratio</t>
+          <t>info_refund_col_time</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>退費比例</t>
+          <t>退費時間</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>問題頁：退費表欄二</t>
+          <t>問題頁：退費表欄一</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>info_privacy_heading</t>
+          <t>info_refund_col_ratio</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>個人資料保護聲明</t>
+          <t>退費比例</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>問題頁：個資標題</t>
+          <t>問題頁：退費表欄二</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>info_privacy_intro</t>
+          <t>info_privacy_heading</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>我們蒐集的個資僅供課程聯繫、保險投保及緊急聯絡使用，絕不提供給第三方。</t>
+          <t>個人資料保護聲明</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>問題頁：個資前言</t>
+          <t>問題頁：個資標題</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>info_privacy_summary</t>
+          <t>info_privacy_intro</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>查看完整聲明</t>
+          <t>我們蒐集的個資僅供課程聯繫、保險投保及緊急聯絡使用，絕不提供給第三方。</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>問題頁：個資摺疊標題</t>
+          <t>問題頁：個資前言</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>info_contact_heading</t>
+          <t>info_privacy_summary</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>聯絡我們</t>
+          <t>查看完整聲明</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>問題頁：聯絡標題</t>
+          <t>問題頁：個資摺疊標題</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>info_contact_line_btn</t>
+          <t>info_contact_heading</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>加 LINE 諮詢</t>
+          <t>聯絡我們</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>問題頁：聯絡 LINE 按鈕</t>
+          <t>問題頁：聯絡標題</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>info_contact_email_btn</t>
+          <t>info_contact_line_btn</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>來信詢問</t>
+          <t>回到 LINE 官方帳號</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>問題頁：聯絡 Email 按鈕</t>
+          <t>問題頁：聯絡 LINE 按鈕</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>info_download_heading</t>
+          <t>info_contact_email_btn</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>檔案下載</t>
+          <t>來信詢問</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>問題頁：下載標題</t>
+          <t>問題頁：聯絡 Email 按鈕</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>info_pdf_title</t>
+          <t>info_download_heading</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>虎甲自然完整簡章 PDF</t>
+          <t>檔案下載</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>問題頁：PDF 卡片標題</t>
+          <t>問題頁：下載標題</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
+          <t>info_pdf_title</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>虎甲自然完整簡章 PDF</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>問題頁：PDF 卡片標題</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
           <t>info_pdf_hint</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>完整版本，可分享給其他家長</t>
         </is>
       </c>
-      <c r="C66" s="8" t="inlineStr">
+      <c r="C67" s="8" t="inlineStr">
         <is>
           <t>問題頁：PDF 卡片說明</t>
         </is>

--- a/data/site.xlsx
+++ b/data/site.xlsx
@@ -1665,7 +1665,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>回到 LINE 官方帳號</t>
+          <t>回到 LINE</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>回到 LINE 官方帳號</t>
+          <t>回到 LINE</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>回到 LINE 官方帳號</t>
+          <t>回到 LINE</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>回到 LINE 官方帳號</t>
+          <t>回到 LINE</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>回到 LINE 官方帳號</t>
+          <t>回到 LINE</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
